--- a/2D Build/gridlock_project_tables_geocoded.xlsx
+++ b/2D Build/gridlock_project_tables_geocoded.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40035CA9-D8F5-4B91-B964-970CD57B0C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46A2E86-BD07-4C17-B8BE-C842BC79476B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DESC Projects" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3221" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="1271">
   <si>
     <t>Project ID</t>
   </si>
@@ -3846,6 +3846,9 @@
   </si>
   <si>
     <t>Sandersville Substation #6</t>
+  </si>
+  <si>
+    <t>Waynesboro Substation</t>
   </si>
 </sst>
 </file>
@@ -13605,16 +13608,16 @@
         <v>693</v>
       </c>
       <c r="J41">
-        <v>39.836285199999999</v>
+        <v>31.635201200000001</v>
       </c>
       <c r="K41">
-        <v>-91.551164799999995</v>
+        <v>-84.212668800000003</v>
       </c>
       <c r="R41">
-        <v>39.836285199999999</v>
+        <v>31.635201200000001</v>
       </c>
       <c r="S41">
-        <v>-91.551164799999995</v>
+        <v>-84.212668800000003</v>
       </c>
       <c r="T41" t="s">
         <v>61</v>
@@ -14533,16 +14536,16 @@
         <v>745</v>
       </c>
       <c r="J58">
-        <v>38.191687999999999</v>
+        <v>31.530909600000001</v>
       </c>
       <c r="K58">
-        <v>-82.604532500000005</v>
+        <v>-82.8779507</v>
       </c>
       <c r="R58">
-        <v>38.191687999999999</v>
+        <v>31.530909600000001</v>
       </c>
       <c r="S58">
-        <v>-82.604532500000005</v>
+        <v>-82.8779507</v>
       </c>
       <c r="T58" t="s">
         <v>61</v>
@@ -19646,26 +19649,29 @@
       <c r="G149" t="s">
         <v>1100</v>
       </c>
+      <c r="I149" t="s">
+        <v>1270</v>
+      </c>
       <c r="J149">
-        <v>36.2053443</v>
+        <v>33.089402900000003</v>
       </c>
       <c r="K149">
-        <v>-86.464917200000002</v>
+        <v>-82.019901000000004</v>
       </c>
       <c r="M149" t="s">
         <v>1101</v>
       </c>
       <c r="O149">
-        <v>43.30827</v>
+        <v>31.4120831</v>
       </c>
       <c r="P149">
-        <v>-112.1217438</v>
+        <v>-82.681688800000003</v>
       </c>
       <c r="R149">
-        <v>36.2053443</v>
+        <v>33.089402900000003</v>
       </c>
       <c r="S149">
-        <v>-86.464917200000002</v>
+        <v>-82.019901000000004</v>
       </c>
       <c r="T149" t="s">
         <v>61</v>
@@ -20465,20 +20471,23 @@
       <c r="G164" t="s">
         <v>1154</v>
       </c>
+      <c r="I164" t="s">
+        <v>1259</v>
+      </c>
       <c r="J164">
-        <v>39.784046199999999</v>
+        <v>33.674044899999998</v>
       </c>
       <c r="K164">
-        <v>-86.304820599999999</v>
+        <v>-83.679252000000005</v>
       </c>
       <c r="R164">
-        <v>39.784046199999999</v>
+        <v>33.674044899999998</v>
       </c>
       <c r="S164">
-        <v>-86.304820599999999</v>
+        <v>-83.679252000000005</v>
       </c>
       <c r="T164" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="U164" t="s">
         <v>156</v>
@@ -20975,16 +20984,16 @@
         <v>1184</v>
       </c>
       <c r="J174">
-        <v>38.599785199999999</v>
+        <v>33.248919299999997</v>
       </c>
       <c r="K174">
-        <v>-90.317619800000003</v>
+        <v>-84.240451800000002</v>
       </c>
       <c r="R174">
-        <v>38.599785199999999</v>
+        <v>33.248919299999997</v>
       </c>
       <c r="S174">
-        <v>-90.317619800000003</v>
+        <v>-84.240451800000002</v>
       </c>
       <c r="T174" t="s">
         <v>30</v>
@@ -21761,19 +21770,19 @@
         <v>1231</v>
       </c>
       <c r="J189">
-        <v>35.795096700000002</v>
+        <v>33.454239999999999</v>
       </c>
       <c r="K189">
-        <v>-86.897985300000002</v>
+        <v>-82.414230000000003</v>
       </c>
       <c r="R189">
-        <v>35.795096700000002</v>
+        <v>33.454239999999999</v>
       </c>
       <c r="S189">
-        <v>-86.897985300000002</v>
+        <v>-82.414230000000003</v>
       </c>
       <c r="T189" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="U189" t="s">
         <v>156</v>
